--- a/table/Datas/#Map.xlsx
+++ b/table/Datas/#Map.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,6 +548,33 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>Assets/Art/Scenes/FlapWangMap.unity</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FlappyRaceMap</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>플래피 레이스 맵</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Assets/Art/Scenes/FlappyRaceMap.unity</t>
         </is>
       </c>
     </row>

--- a/table/Datas/#Map.xlsx
+++ b/table/Datas/#Map.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,15 +486,11 @@
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -575,6 +571,29 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>Assets/Art/Scenes/FlappyRaceMap.unity</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PanchigiMap</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>판치기 맵</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Assets/Art/Scenes/PanchigiMap.unity</t>
         </is>
       </c>
     </row>

--- a/table/Datas/#Map.xlsx
+++ b/table/Datas/#Map.xlsx
@@ -593,7 +593,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Assets/Art/Scenes/PanchigiMap.unity</t>
+          <t>Assets/Art/Scenes/FlapWangMap.unity</t>
         </is>
       </c>
     </row>

--- a/table/Datas/#Map.xlsx
+++ b/table/Datas/#Map.xlsx
@@ -593,7 +593,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Assets/Art/Scenes/FlapWangMap.unity</t>
+          <t>Assets/Art/Scenes/PanchigiMap.unity</t>
         </is>
       </c>
     </row>

--- a/table/Datas/#Map.xlsx
+++ b/table/Datas/#Map.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,6 +597,30 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SkydiveMap</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>스카이다이브 맵</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Assets/Art/Scenes/SkydiveMap.unity</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/#Map.xlsx
+++ b/table/Datas/#Map.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -598,7 +598,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
         <v>4</v>
       </c>
@@ -618,6 +617,29 @@
       <c r="F8" t="inlineStr">
         <is>
           <t>Assets/Art/Scenes/SkydiveMap.unity</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>archery_circle</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>원형 사대</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Assets/Art/Scenes/ArcheryCircleMap.unity</t>
         </is>
       </c>
     </row>
